--- a/mom/docs/forms/frm-500-production/FRM-526_Daily_Machine_Startup_and_Autonomous_Maintenance_Check.xlsx
+++ b/mom/docs/forms/frm-500-production/FRM-526_Daily_Machine_Startup_and_Autonomous_Maintenance_Check.xlsx
@@ -490,14 +490,14 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="0064748B"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="001E3A8A"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -774,14 +774,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
@@ -3674,7 +3674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="523">
+  <cellXfs count="520">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4877,13 +4877,13 @@
     <xf numFmtId="0" fontId="79" fillId="49" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="49" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="82" fillId="51" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="49" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="83" fillId="49" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4892,23 +4892,24 @@
     <xf numFmtId="0" fontId="80" fillId="47" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="51" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="52" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="52" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="53" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="51" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="52" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="49" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="80" fillId="47" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5039,6 +5040,40 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Bảo trì phòng ngừa gần nhất
+Số phiếu FRM-521 của lần PM gần nhất.</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>Nồng độ coolant
+Đo bằng khúc xạ kế — phải trong dải mục tiêu.</t>
+      </text>
+    </comment>
+    <comment ref="AF15" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS / HOLD / FAIL — chọn từ danh sách.</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra an toàn
+Hạng mục SAF — nếu FAIL phải dừng máy ngay, không được vận hành.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5363,7 +5398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BS43"/>
+  <dimension ref="A2:AN41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5609,7 +5644,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="522" t="n"/>
+      <c r="A7" s="519" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -5653,7 +5688,7 @@
     <row r="8" ht="17" customHeight="1" s="264">
       <c r="A8" s="470" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.  REFERENCE INFORMATION</t>
+          <t xml:space="preserve">  1.  MACHINE &amp; SHIFT HEADER</t>
         </is>
       </c>
       <c r="B8" s="471" t="n"/>
@@ -5797,282 +5832,275 @@
       <c r="AN10" s="486" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="264">
-      <c r="A11" s="487" t="inlineStr">
+      <c r="A11" s="480" t="inlineStr">
         <is>
           <t>Last PM Ref (FRM-521)</t>
         </is>
       </c>
-      <c r="B11" s="488" t="n"/>
-      <c r="C11" s="488" t="n"/>
-      <c r="D11" s="488" t="n"/>
-      <c r="E11" s="488" t="n"/>
-      <c r="F11" s="488" t="n"/>
-      <c r="G11" s="489" t="n"/>
-      <c r="H11" s="490" t="n"/>
-      <c r="I11" s="488" t="n"/>
-      <c r="J11" s="488" t="n"/>
-      <c r="K11" s="488" t="n"/>
-      <c r="L11" s="488" t="n"/>
-      <c r="M11" s="488" t="n"/>
-      <c r="N11" s="488" t="n"/>
-      <c r="O11" s="488" t="n"/>
-      <c r="P11" s="488" t="n"/>
-      <c r="Q11" s="488" t="n"/>
-      <c r="R11" s="488" t="n"/>
-      <c r="S11" s="488" t="n"/>
-      <c r="T11" s="489" t="n"/>
-      <c r="U11" s="491" t="inlineStr">
+      <c r="B11" s="481" t="n"/>
+      <c r="C11" s="481" t="n"/>
+      <c r="D11" s="481" t="n"/>
+      <c r="E11" s="481" t="n"/>
+      <c r="F11" s="481" t="n"/>
+      <c r="G11" s="482" t="n"/>
+      <c r="H11" s="483" t="n"/>
+      <c r="I11" s="481" t="n"/>
+      <c r="J11" s="481" t="n"/>
+      <c r="K11" s="481" t="n"/>
+      <c r="L11" s="481" t="n"/>
+      <c r="M11" s="481" t="n"/>
+      <c r="N11" s="481" t="n"/>
+      <c r="O11" s="481" t="n"/>
+      <c r="P11" s="481" t="n"/>
+      <c r="Q11" s="481" t="n"/>
+      <c r="R11" s="481" t="n"/>
+      <c r="S11" s="481" t="n"/>
+      <c r="T11" s="482" t="n"/>
+      <c r="U11" s="484" t="inlineStr">
         <is>
           <t>Coolant Concentration (%)</t>
         </is>
       </c>
-      <c r="V11" s="488" t="n"/>
-      <c r="W11" s="488" t="n"/>
-      <c r="X11" s="488" t="n"/>
-      <c r="Y11" s="488" t="n"/>
-      <c r="Z11" s="488" t="n"/>
-      <c r="AA11" s="489" t="n"/>
-      <c r="AB11" s="492" t="n"/>
-      <c r="AC11" s="488" t="n"/>
-      <c r="AD11" s="488" t="n"/>
-      <c r="AE11" s="488" t="n"/>
-      <c r="AF11" s="488" t="n"/>
-      <c r="AG11" s="488" t="n"/>
-      <c r="AH11" s="488" t="n"/>
-      <c r="AI11" s="488" t="n"/>
-      <c r="AJ11" s="488" t="n"/>
-      <c r="AK11" s="488" t="n"/>
-      <c r="AL11" s="488" t="n"/>
-      <c r="AM11" s="488" t="n"/>
-      <c r="AN11" s="493" t="n"/>
+      <c r="V11" s="481" t="n"/>
+      <c r="W11" s="481" t="n"/>
+      <c r="X11" s="481" t="n"/>
+      <c r="Y11" s="481" t="n"/>
+      <c r="Z11" s="481" t="n"/>
+      <c r="AA11" s="482" t="n"/>
+      <c r="AB11" s="485" t="n"/>
+      <c r="AC11" s="481" t="n"/>
+      <c r="AD11" s="481" t="n"/>
+      <c r="AE11" s="481" t="n"/>
+      <c r="AF11" s="481" t="n"/>
+      <c r="AG11" s="481" t="n"/>
+      <c r="AH11" s="481" t="n"/>
+      <c r="AI11" s="481" t="n"/>
+      <c r="AJ11" s="481" t="n"/>
+      <c r="AK11" s="481" t="n"/>
+      <c r="AL11" s="481" t="n"/>
+      <c r="AM11" s="481" t="n"/>
+      <c r="AN11" s="486" t="n"/>
     </row>
-    <row r="12" ht="4" customHeight="1" s="264">
-      <c r="A12" s="522" t="n"/>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="26" t="n"/>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="26" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="26" t="n"/>
-      <c r="AB12" s="26" t="n"/>
-      <c r="AC12" s="26" t="n"/>
-      <c r="AD12" s="26" t="n"/>
-      <c r="AE12" s="26" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="26" t="n"/>
-      <c r="AH12" s="26" t="n"/>
-      <c r="AI12" s="26" t="n"/>
-      <c r="AJ12" s="26" t="n"/>
-      <c r="AK12" s="26" t="n"/>
-      <c r="AL12" s="26" t="n"/>
-      <c r="AM12" s="26" t="n"/>
-      <c r="AN12" s="26" t="n"/>
+    <row r="12" ht="20" customHeight="1" s="264">
+      <c r="A12" s="487" t="inlineStr">
+        <is>
+          <t>Hour-Meter Reading</t>
+        </is>
+      </c>
+      <c r="B12" s="488" t="n"/>
+      <c r="C12" s="488" t="n"/>
+      <c r="D12" s="488" t="n"/>
+      <c r="E12" s="488" t="n"/>
+      <c r="F12" s="488" t="n"/>
+      <c r="G12" s="489" t="n"/>
+      <c r="H12" s="490" t="n"/>
+      <c r="I12" s="488" t="n"/>
+      <c r="J12" s="488" t="n"/>
+      <c r="K12" s="488" t="n"/>
+      <c r="L12" s="488" t="n"/>
+      <c r="M12" s="488" t="n"/>
+      <c r="N12" s="488" t="n"/>
+      <c r="O12" s="488" t="n"/>
+      <c r="P12" s="488" t="n"/>
+      <c r="Q12" s="488" t="n"/>
+      <c r="R12" s="488" t="n"/>
+      <c r="S12" s="488" t="n"/>
+      <c r="T12" s="489" t="n"/>
+      <c r="U12" s="491" t="inlineStr">
+        <is>
+          <t>Linked FRM-721 Line Clearance</t>
+        </is>
+      </c>
+      <c r="V12" s="488" t="n"/>
+      <c r="W12" s="488" t="n"/>
+      <c r="X12" s="488" t="n"/>
+      <c r="Y12" s="488" t="n"/>
+      <c r="Z12" s="488" t="n"/>
+      <c r="AA12" s="489" t="n"/>
+      <c r="AB12" s="492" t="n"/>
+      <c r="AC12" s="488" t="n"/>
+      <c r="AD12" s="488" t="n"/>
+      <c r="AE12" s="488" t="n"/>
+      <c r="AF12" s="488" t="n"/>
+      <c r="AG12" s="488" t="n"/>
+      <c r="AH12" s="488" t="n"/>
+      <c r="AI12" s="488" t="n"/>
+      <c r="AJ12" s="488" t="n"/>
+      <c r="AK12" s="488" t="n"/>
+      <c r="AL12" s="488" t="n"/>
+      <c r="AM12" s="488" t="n"/>
+      <c r="AN12" s="493" t="n"/>
     </row>
-    <row r="13" ht="17" customHeight="1" s="264">
-      <c r="A13" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2.  STARTUP &amp; AUTONOMOUS MAINTENANCE CHECKLIST</t>
-        </is>
-      </c>
-      <c r="B13" s="471" t="n"/>
-      <c r="C13" s="471" t="n"/>
-      <c r="D13" s="471" t="n"/>
-      <c r="E13" s="471" t="n"/>
-      <c r="F13" s="471" t="n"/>
-      <c r="G13" s="471" t="n"/>
-      <c r="H13" s="471" t="n"/>
-      <c r="I13" s="471" t="n"/>
-      <c r="J13" s="471" t="n"/>
-      <c r="K13" s="471" t="n"/>
-      <c r="L13" s="471" t="n"/>
-      <c r="M13" s="471" t="n"/>
-      <c r="N13" s="471" t="n"/>
-      <c r="O13" s="471" t="n"/>
-      <c r="P13" s="471" t="n"/>
-      <c r="Q13" s="471" t="n"/>
-      <c r="R13" s="471" t="n"/>
-      <c r="S13" s="471" t="n"/>
-      <c r="T13" s="471" t="n"/>
-      <c r="U13" s="471" t="n"/>
-      <c r="V13" s="471" t="n"/>
-      <c r="W13" s="471" t="n"/>
-      <c r="X13" s="471" t="n"/>
-      <c r="Y13" s="471" t="n"/>
-      <c r="Z13" s="471" t="n"/>
-      <c r="AA13" s="471" t="n"/>
-      <c r="AB13" s="471" t="n"/>
-      <c r="AC13" s="471" t="n"/>
-      <c r="AD13" s="471" t="n"/>
-      <c r="AE13" s="471" t="n"/>
-      <c r="AF13" s="471" t="n"/>
-      <c r="AG13" s="471" t="n"/>
-      <c r="AH13" s="471" t="n"/>
-      <c r="AI13" s="471" t="n"/>
-      <c r="AJ13" s="471" t="n"/>
-      <c r="AK13" s="471" t="n"/>
-      <c r="AL13" s="471" t="n"/>
-      <c r="AM13" s="471" t="n"/>
-      <c r="AN13" s="472" t="n"/>
+    <row r="13" ht="4" customHeight="1" s="264">
+      <c r="A13" s="519" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="26" t="n"/>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="26" t="n"/>
+      <c r="O13" s="26" t="n"/>
+      <c r="P13" s="26" t="n"/>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="26" t="n"/>
+      <c r="S13" s="26" t="n"/>
+      <c r="T13" s="26" t="n"/>
+      <c r="U13" s="26" t="n"/>
+      <c r="V13" s="26" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="26" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="26" t="n"/>
+      <c r="AB13" s="26" t="n"/>
+      <c r="AC13" s="26" t="n"/>
+      <c r="AD13" s="26" t="n"/>
+      <c r="AE13" s="26" t="n"/>
+      <c r="AF13" s="26" t="n"/>
+      <c r="AG13" s="26" t="n"/>
+      <c r="AH13" s="26" t="n"/>
+      <c r="AI13" s="26" t="n"/>
+      <c r="AJ13" s="26" t="n"/>
+      <c r="AK13" s="26" t="n"/>
+      <c r="AL13" s="26" t="n"/>
+      <c r="AM13" s="26" t="n"/>
+      <c r="AN13" s="26" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1" s="264">
-      <c r="A14" s="494" t="inlineStr">
+      <c r="A14" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2.  STARTUP &amp; AUTONOMOUS MAINTENANCE CHECKLIST</t>
+        </is>
+      </c>
+      <c r="B14" s="471" t="n"/>
+      <c r="C14" s="471" t="n"/>
+      <c r="D14" s="471" t="n"/>
+      <c r="E14" s="471" t="n"/>
+      <c r="F14" s="471" t="n"/>
+      <c r="G14" s="471" t="n"/>
+      <c r="H14" s="471" t="n"/>
+      <c r="I14" s="471" t="n"/>
+      <c r="J14" s="471" t="n"/>
+      <c r="K14" s="471" t="n"/>
+      <c r="L14" s="471" t="n"/>
+      <c r="M14" s="471" t="n"/>
+      <c r="N14" s="471" t="n"/>
+      <c r="O14" s="471" t="n"/>
+      <c r="P14" s="471" t="n"/>
+      <c r="Q14" s="471" t="n"/>
+      <c r="R14" s="471" t="n"/>
+      <c r="S14" s="471" t="n"/>
+      <c r="T14" s="471" t="n"/>
+      <c r="U14" s="471" t="n"/>
+      <c r="V14" s="471" t="n"/>
+      <c r="W14" s="471" t="n"/>
+      <c r="X14" s="471" t="n"/>
+      <c r="Y14" s="471" t="n"/>
+      <c r="Z14" s="471" t="n"/>
+      <c r="AA14" s="471" t="n"/>
+      <c r="AB14" s="471" t="n"/>
+      <c r="AC14" s="471" t="n"/>
+      <c r="AD14" s="471" t="n"/>
+      <c r="AE14" s="471" t="n"/>
+      <c r="AF14" s="471" t="n"/>
+      <c r="AG14" s="471" t="n"/>
+      <c r="AH14" s="471" t="n"/>
+      <c r="AI14" s="471" t="n"/>
+      <c r="AJ14" s="471" t="n"/>
+      <c r="AK14" s="471" t="n"/>
+      <c r="AL14" s="471" t="n"/>
+      <c r="AM14" s="471" t="n"/>
+      <c r="AN14" s="472" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1" s="264">
+      <c r="A15" s="494" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="475" t="n"/>
-      <c r="C14" s="495" t="inlineStr">
+      <c r="B15" s="475" t="n"/>
+      <c r="C15" s="495" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D14" s="474" t="n"/>
-      <c r="E14" s="475" t="n"/>
-      <c r="F14" s="495" t="inlineStr">
+      <c r="D15" s="474" t="n"/>
+      <c r="E15" s="475" t="n"/>
+      <c r="F15" s="495" t="inlineStr">
         <is>
           <t>Startup / AM Check Item</t>
         </is>
       </c>
-      <c r="G14" s="474" t="n"/>
-      <c r="H14" s="474" t="n"/>
-      <c r="I14" s="474" t="n"/>
-      <c r="J14" s="474" t="n"/>
-      <c r="K14" s="474" t="n"/>
-      <c r="L14" s="474" t="n"/>
-      <c r="M14" s="474" t="n"/>
-      <c r="N14" s="474" t="n"/>
-      <c r="O14" s="474" t="n"/>
-      <c r="P14" s="474" t="n"/>
-      <c r="Q14" s="474" t="n"/>
-      <c r="R14" s="474" t="n"/>
-      <c r="S14" s="474" t="n"/>
-      <c r="T14" s="474" t="n"/>
-      <c r="U14" s="475" t="n"/>
-      <c r="V14" s="495" t="inlineStr">
-        <is>
-          <t>Acceptance / Control Rule</t>
-        </is>
-      </c>
-      <c r="W14" s="474" t="n"/>
-      <c r="X14" s="474" t="n"/>
-      <c r="Y14" s="474" t="n"/>
-      <c r="Z14" s="474" t="n"/>
-      <c r="AA14" s="474" t="n"/>
-      <c r="AB14" s="474" t="n"/>
-      <c r="AC14" s="474" t="n"/>
-      <c r="AD14" s="474" t="n"/>
-      <c r="AE14" s="475" t="n"/>
-      <c r="AF14" s="495" t="inlineStr">
+      <c r="G15" s="474" t="n"/>
+      <c r="H15" s="474" t="n"/>
+      <c r="I15" s="474" t="n"/>
+      <c r="J15" s="474" t="n"/>
+      <c r="K15" s="474" t="n"/>
+      <c r="L15" s="474" t="n"/>
+      <c r="M15" s="474" t="n"/>
+      <c r="N15" s="474" t="n"/>
+      <c r="O15" s="474" t="n"/>
+      <c r="P15" s="474" t="n"/>
+      <c r="Q15" s="474" t="n"/>
+      <c r="R15" s="474" t="n"/>
+      <c r="S15" s="474" t="n"/>
+      <c r="T15" s="474" t="n"/>
+      <c r="U15" s="475" t="n"/>
+      <c r="V15" s="495" t="inlineStr">
+        <is>
+          <t>Standard / Acceptance</t>
+        </is>
+      </c>
+      <c r="W15" s="474" t="n"/>
+      <c r="X15" s="474" t="n"/>
+      <c r="Y15" s="474" t="n"/>
+      <c r="Z15" s="474" t="n"/>
+      <c r="AA15" s="474" t="n"/>
+      <c r="AB15" s="474" t="n"/>
+      <c r="AC15" s="474" t="n"/>
+      <c r="AD15" s="474" t="n"/>
+      <c r="AE15" s="475" t="n"/>
+      <c r="AF15" s="495" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG14" s="474" t="n"/>
-      <c r="AH14" s="474" t="n"/>
-      <c r="AI14" s="475" t="n"/>
-      <c r="AJ14" s="496" t="inlineStr">
+      <c r="AG15" s="474" t="n"/>
+      <c r="AH15" s="474" t="n"/>
+      <c r="AI15" s="475" t="n"/>
+      <c r="AJ15" s="496" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK14" s="474" t="n"/>
-      <c r="AL14" s="474" t="n"/>
-      <c r="AM14" s="474" t="n"/>
-      <c r="AN14" s="479" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
-        <v/>
-      </c>
-      <c r="B15" s="482" t="n"/>
-      <c r="C15" s="498" t="inlineStr">
-        <is>
-          <t>MNT</t>
-        </is>
-      </c>
-      <c r="D15" s="481" t="n"/>
-      <c r="E15" s="482" t="n"/>
-      <c r="F15" s="499" t="inlineStr">
-        <is>
-          <t>Way-lube / slideway lubricant level adequate.</t>
-        </is>
-      </c>
-      <c r="G15" s="481" t="n"/>
-      <c r="H15" s="481" t="n"/>
-      <c r="I15" s="481" t="n"/>
-      <c r="J15" s="481" t="n"/>
-      <c r="K15" s="481" t="n"/>
-      <c r="L15" s="481" t="n"/>
-      <c r="M15" s="481" t="n"/>
-      <c r="N15" s="481" t="n"/>
-      <c r="O15" s="481" t="n"/>
-      <c r="P15" s="481" t="n"/>
-      <c r="Q15" s="481" t="n"/>
-      <c r="R15" s="481" t="n"/>
-      <c r="S15" s="481" t="n"/>
-      <c r="T15" s="481" t="n"/>
-      <c r="U15" s="482" t="n"/>
-      <c r="V15" s="500" t="inlineStr">
-        <is>
-          <t>Above minimum sight-glass mark.</t>
-        </is>
-      </c>
-      <c r="W15" s="481" t="n"/>
-      <c r="X15" s="481" t="n"/>
-      <c r="Y15" s="481" t="n"/>
-      <c r="Z15" s="481" t="n"/>
-      <c r="AA15" s="481" t="n"/>
-      <c r="AB15" s="481" t="n"/>
-      <c r="AC15" s="481" t="n"/>
-      <c r="AD15" s="481" t="n"/>
-      <c r="AE15" s="482" t="n"/>
-      <c r="AF15" s="501" t="n"/>
-      <c r="AG15" s="481" t="n"/>
-      <c r="AH15" s="481" t="n"/>
-      <c r="AI15" s="482" t="n"/>
-      <c r="AJ15" s="502" t="n"/>
-      <c r="AK15" s="481" t="n"/>
-      <c r="AL15" s="481" t="n"/>
-      <c r="AM15" s="481" t="n"/>
-      <c r="AN15" s="486" t="n"/>
+      <c r="AK15" s="474" t="n"/>
+      <c r="AL15" s="474" t="n"/>
+      <c r="AM15" s="474" t="n"/>
+      <c r="AN15" s="479" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
       <c r="A16" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B16" s="482" t="n"/>
       <c r="C16" s="498" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D16" s="481" t="n"/>
       <c r="E16" s="482" t="n"/>
-      <c r="F16" s="503" t="inlineStr">
-        <is>
-          <t>Hydraulic oil level and pressure normal.</t>
+      <c r="F16" s="499" t="inlineStr">
+        <is>
+          <t>Way-lube / slideway lubricant level adequate.</t>
         </is>
       </c>
       <c r="G16" s="481" t="n"/>
@@ -6092,7 +6120,7 @@
       <c r="U16" s="482" t="n"/>
       <c r="V16" s="500" t="inlineStr">
         <is>
-          <t>Within gauge green band.</t>
+          <t>Above minimum sight-glass mark.</t>
         </is>
       </c>
       <c r="W16" s="481" t="n"/>
@@ -6116,20 +6144,20 @@
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
       <c r="A17" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B17" s="482" t="n"/>
       <c r="C17" s="498" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D17" s="481" t="n"/>
       <c r="E17" s="482" t="n"/>
-      <c r="F17" s="499" t="inlineStr">
-        <is>
-          <t>Pneumatic air supply pressure within range.</t>
+      <c r="F17" s="503" t="inlineStr">
+        <is>
+          <t>Hydraulic oil level and pressure normal.</t>
         </is>
       </c>
       <c r="G17" s="481" t="n"/>
@@ -6149,7 +6177,7 @@
       <c r="U17" s="482" t="n"/>
       <c r="V17" s="500" t="inlineStr">
         <is>
-          <t>Per machine nameplate spec.</t>
+          <t>Within gauge green band.</t>
         </is>
       </c>
       <c r="W17" s="481" t="n"/>
@@ -6173,20 +6201,20 @@
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
       <c r="A18" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B18" s="482" t="n"/>
       <c r="C18" s="498" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D18" s="481" t="n"/>
       <c r="E18" s="482" t="n"/>
-      <c r="F18" s="503" t="inlineStr">
-        <is>
-          <t>Coolant level and concentration verified.</t>
+      <c r="F18" s="499" t="inlineStr">
+        <is>
+          <t>Pneumatic air-supply pressure within range.</t>
         </is>
       </c>
       <c r="G18" s="481" t="n"/>
@@ -6206,7 +6234,7 @@
       <c r="U18" s="482" t="n"/>
       <c r="V18" s="500" t="inlineStr">
         <is>
-          <t>Refractometer reading within target band.</t>
+          <t>Per machine nameplate spec.</t>
         </is>
       </c>
       <c r="W18" s="481" t="n"/>
@@ -6230,20 +6258,20 @@
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
       <c r="A19" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B19" s="482" t="n"/>
       <c r="C19" s="498" t="inlineStr">
         <is>
-          <t>MNT</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D19" s="481" t="n"/>
       <c r="E19" s="482" t="n"/>
-      <c r="F19" s="499" t="inlineStr">
-        <is>
-          <t>Coolant filtration / chip conveyor functional.</t>
+      <c r="F19" s="503" t="inlineStr">
+        <is>
+          <t>Coolant level and concentration verified.</t>
         </is>
       </c>
       <c r="G19" s="481" t="n"/>
@@ -6263,7 +6291,7 @@
       <c r="U19" s="482" t="n"/>
       <c r="V19" s="500" t="inlineStr">
         <is>
-          <t>No blockage; conveyor runs free.</t>
+          <t>Refractometer reading within target band.</t>
         </is>
       </c>
       <c r="W19" s="481" t="n"/>
@@ -6287,20 +6315,20 @@
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
       <c r="A20" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B20" s="482" t="n"/>
-      <c r="C20" s="504" t="inlineStr">
+      <c r="C20" s="498" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
       <c r="D20" s="481" t="n"/>
       <c r="E20" s="482" t="n"/>
-      <c r="F20" s="503" t="inlineStr">
-        <is>
-          <t>Spindle warm-up cycle completed.</t>
+      <c r="F20" s="499" t="inlineStr">
+        <is>
+          <t>Coolant filtration / chip conveyor functional.</t>
         </is>
       </c>
       <c r="G20" s="481" t="n"/>
@@ -6320,7 +6348,7 @@
       <c r="U20" s="482" t="n"/>
       <c r="V20" s="500" t="inlineStr">
         <is>
-          <t>Per machine warm-up program.</t>
+          <t>No blockage; conveyor runs free.</t>
         </is>
       </c>
       <c r="W20" s="481" t="n"/>
@@ -6344,20 +6372,20 @@
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
       <c r="A21" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B21" s="482" t="n"/>
-      <c r="C21" s="504" t="inlineStr">
+      <c r="C21" s="498" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
       <c r="D21" s="481" t="n"/>
       <c r="E21" s="482" t="n"/>
-      <c r="F21" s="499" t="inlineStr">
-        <is>
-          <t>All axes homed / referenced correctly.</t>
+      <c r="F21" s="503" t="inlineStr">
+        <is>
+          <t>Spindle warm-up cycle completed.</t>
         </is>
       </c>
       <c r="G21" s="481" t="n"/>
@@ -6377,7 +6405,7 @@
       <c r="U21" s="482" t="n"/>
       <c r="V21" s="500" t="inlineStr">
         <is>
-          <t>Reference return completed without alarm.</t>
+          <t>Per machine warm-up program.</t>
         </is>
       </c>
       <c r="W21" s="481" t="n"/>
@@ -6401,20 +6429,20 @@
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
       <c r="A22" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B22" s="482" t="n"/>
-      <c r="C22" s="505" t="inlineStr">
-        <is>
-          <t>SAF</t>
+      <c r="C22" s="498" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D22" s="481" t="n"/>
       <c r="E22" s="482" t="n"/>
-      <c r="F22" s="503" t="inlineStr">
-        <is>
-          <t>Guards, doors and interlocks functional.</t>
+      <c r="F22" s="499" t="inlineStr">
+        <is>
+          <t>All axes homed / referenced correctly.</t>
         </is>
       </c>
       <c r="G22" s="481" t="n"/>
@@ -6434,7 +6462,7 @@
       <c r="U22" s="482" t="n"/>
       <c r="V22" s="500" t="inlineStr">
         <is>
-          <t>Door interlock stops motion when opened.</t>
+          <t>Reference return completed without alarm.</t>
         </is>
       </c>
       <c r="W22" s="481" t="n"/>
@@ -6458,20 +6486,20 @@
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
       <c r="A23" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B23" s="482" t="n"/>
-      <c r="C23" s="505" t="inlineStr">
+      <c r="C23" s="504" t="inlineStr">
         <is>
           <t>SAF</t>
         </is>
       </c>
       <c r="D23" s="481" t="n"/>
       <c r="E23" s="482" t="n"/>
-      <c r="F23" s="499" t="inlineStr">
-        <is>
-          <t>Emergency-stop tested and resets correctly.</t>
+      <c r="F23" s="503" t="inlineStr">
+        <is>
+          <t>Guards, doors and interlocks functional.</t>
         </is>
       </c>
       <c r="G23" s="481" t="n"/>
@@ -6491,7 +6519,7 @@
       <c r="U23" s="482" t="n"/>
       <c r="V23" s="500" t="inlineStr">
         <is>
-          <t>E-stop halts all motion; resets cleanly.</t>
+          <t>Door interlock stops motion when opened.</t>
         </is>
       </c>
       <c r="W23" s="481" t="n"/>
@@ -6515,20 +6543,20 @@
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
       <c r="A24" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B24" s="482" t="n"/>
-      <c r="C24" s="498" t="inlineStr">
-        <is>
-          <t>MNT</t>
+      <c r="C24" s="504" t="inlineStr">
+        <is>
+          <t>SAF</t>
         </is>
       </c>
       <c r="D24" s="481" t="n"/>
       <c r="E24" s="482" t="n"/>
-      <c r="F24" s="503" t="inlineStr">
-        <is>
-          <t>Daily lubrication / grease points serviced.</t>
+      <c r="F24" s="499" t="inlineStr">
+        <is>
+          <t>Emergency-stop tested and resets correctly.</t>
         </is>
       </c>
       <c r="G24" s="481" t="n"/>
@@ -6548,7 +6576,7 @@
       <c r="U24" s="482" t="n"/>
       <c r="V24" s="500" t="inlineStr">
         <is>
-          <t>Per machine lube chart.</t>
+          <t>E-stop halts all motion; resets cleanly.</t>
         </is>
       </c>
       <c r="W24" s="481" t="n"/>
@@ -6572,20 +6600,20 @@
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
       <c r="A25" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B25" s="482" t="n"/>
-      <c r="C25" s="504" t="inlineStr">
+      <c r="C25" s="498" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
       <c r="D25" s="481" t="n"/>
       <c r="E25" s="482" t="n"/>
-      <c r="F25" s="499" t="inlineStr">
-        <is>
-          <t>Work area clean and FOD-free.</t>
+      <c r="F25" s="503" t="inlineStr">
+        <is>
+          <t>Daily lubrication / grease points serviced.</t>
         </is>
       </c>
       <c r="G25" s="481" t="n"/>
@@ -6605,7 +6633,7 @@
       <c r="U25" s="482" t="n"/>
       <c r="V25" s="500" t="inlineStr">
         <is>
-          <t>Line clearance per FRM-721.</t>
+          <t>Per machine lube chart.</t>
         </is>
       </c>
       <c r="W25" s="481" t="n"/>
@@ -6629,20 +6657,20 @@
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
       <c r="A26" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B26" s="482" t="n"/>
-      <c r="C26" s="504" t="inlineStr">
+      <c r="C26" s="498" t="inlineStr">
         <is>
           <t>OPS</t>
         </is>
       </c>
       <c r="D26" s="481" t="n"/>
       <c r="E26" s="482" t="n"/>
-      <c r="F26" s="503" t="inlineStr">
-        <is>
-          <t>No active alarms; controller status normal.</t>
+      <c r="F26" s="499" t="inlineStr">
+        <is>
+          <t>Work area clean and FOD-free.</t>
         </is>
       </c>
       <c r="G26" s="481" t="n"/>
@@ -6662,7 +6690,7 @@
       <c r="U26" s="482" t="n"/>
       <c r="V26" s="500" t="inlineStr">
         <is>
-          <t>Alarm history reviewed and cleared.</t>
+          <t>Line clearance per FRM-721.</t>
         </is>
       </c>
       <c r="W26" s="481" t="n"/>
@@ -6686,20 +6714,20 @@
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
       <c r="A27" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B27" s="482" t="n"/>
-      <c r="C27" s="505" t="inlineStr">
-        <is>
-          <t>TOOL</t>
+      <c r="C27" s="498" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D27" s="481" t="n"/>
       <c r="E27" s="482" t="n"/>
-      <c r="F27" s="499" t="inlineStr">
-        <is>
-          <t>Tool magazine / ATC operates correctly.</t>
+      <c r="F27" s="503" t="inlineStr">
+        <is>
+          <t>No active alarms; controller status normal.</t>
         </is>
       </c>
       <c r="G27" s="481" t="n"/>
@@ -6719,7 +6747,7 @@
       <c r="U27" s="482" t="n"/>
       <c r="V27" s="500" t="inlineStr">
         <is>
-          <t>Random tool-change cycle verified.</t>
+          <t>Alarm history reviewed and cleared.</t>
         </is>
       </c>
       <c r="W27" s="481" t="n"/>
@@ -6743,20 +6771,20 @@
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
       <c r="A28" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
       <c r="B28" s="482" t="n"/>
-      <c r="C28" s="498" t="inlineStr">
-        <is>
-          <t>MNT</t>
+      <c r="C28" s="504" t="inlineStr">
+        <is>
+          <t>TOOL</t>
         </is>
       </c>
       <c r="D28" s="481" t="n"/>
       <c r="E28" s="482" t="n"/>
-      <c r="F28" s="503" t="inlineStr">
-        <is>
-          <t>No abnormal noise, vibration or fluid leak.</t>
+      <c r="F28" s="499" t="inlineStr">
+        <is>
+          <t>Tool magazine / ATC operates correctly.</t>
         </is>
       </c>
       <c r="G28" s="481" t="n"/>
@@ -6776,7 +6804,7 @@
       <c r="U28" s="482" t="n"/>
       <c r="V28" s="500" t="inlineStr">
         <is>
-          <t>Visual + audible check before production.</t>
+          <t>Random tool-change cycle verified.</t>
         </is>
       </c>
       <c r="W28" s="481" t="n"/>
@@ -6799,698 +6827,617 @@
       <c r="AN28" s="486" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="264">
-      <c r="A29" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
+      <c r="A29" s="505">
+        <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B29" s="482" t="n"/>
-      <c r="C29" s="506" t="n"/>
-      <c r="D29" s="481" t="n"/>
-      <c r="E29" s="482" t="n"/>
-      <c r="F29" s="507" t="n"/>
-      <c r="G29" s="481" t="n"/>
-      <c r="H29" s="481" t="n"/>
-      <c r="I29" s="481" t="n"/>
-      <c r="J29" s="481" t="n"/>
-      <c r="K29" s="481" t="n"/>
-      <c r="L29" s="481" t="n"/>
-      <c r="M29" s="481" t="n"/>
-      <c r="N29" s="481" t="n"/>
-      <c r="O29" s="481" t="n"/>
-      <c r="P29" s="481" t="n"/>
-      <c r="Q29" s="481" t="n"/>
-      <c r="R29" s="481" t="n"/>
-      <c r="S29" s="481" t="n"/>
-      <c r="T29" s="481" t="n"/>
-      <c r="U29" s="482" t="n"/>
-      <c r="V29" s="506" t="n"/>
-      <c r="W29" s="481" t="n"/>
-      <c r="X29" s="481" t="n"/>
-      <c r="Y29" s="481" t="n"/>
-      <c r="Z29" s="481" t="n"/>
-      <c r="AA29" s="481" t="n"/>
-      <c r="AB29" s="481" t="n"/>
-      <c r="AC29" s="481" t="n"/>
-      <c r="AD29" s="481" t="n"/>
-      <c r="AE29" s="482" t="n"/>
-      <c r="AF29" s="501" t="n"/>
-      <c r="AG29" s="481" t="n"/>
-      <c r="AH29" s="481" t="n"/>
-      <c r="AI29" s="482" t="n"/>
-      <c r="AJ29" s="502" t="n"/>
-      <c r="AK29" s="481" t="n"/>
-      <c r="AL29" s="481" t="n"/>
-      <c r="AM29" s="481" t="n"/>
-      <c r="AN29" s="486" t="n"/>
+      <c r="B29" s="489" t="n"/>
+      <c r="C29" s="506" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="D29" s="488" t="n"/>
+      <c r="E29" s="489" t="n"/>
+      <c r="F29" s="507" t="inlineStr">
+        <is>
+          <t>No abnormal noise, vibration or fluid leak.</t>
+        </is>
+      </c>
+      <c r="G29" s="488" t="n"/>
+      <c r="H29" s="488" t="n"/>
+      <c r="I29" s="488" t="n"/>
+      <c r="J29" s="488" t="n"/>
+      <c r="K29" s="488" t="n"/>
+      <c r="L29" s="488" t="n"/>
+      <c r="M29" s="488" t="n"/>
+      <c r="N29" s="488" t="n"/>
+      <c r="O29" s="488" t="n"/>
+      <c r="P29" s="488" t="n"/>
+      <c r="Q29" s="488" t="n"/>
+      <c r="R29" s="488" t="n"/>
+      <c r="S29" s="488" t="n"/>
+      <c r="T29" s="488" t="n"/>
+      <c r="U29" s="489" t="n"/>
+      <c r="V29" s="508" t="inlineStr">
+        <is>
+          <t>Visual + audible check before production.</t>
+        </is>
+      </c>
+      <c r="W29" s="488" t="n"/>
+      <c r="X29" s="488" t="n"/>
+      <c r="Y29" s="488" t="n"/>
+      <c r="Z29" s="488" t="n"/>
+      <c r="AA29" s="488" t="n"/>
+      <c r="AB29" s="488" t="n"/>
+      <c r="AC29" s="488" t="n"/>
+      <c r="AD29" s="488" t="n"/>
+      <c r="AE29" s="489" t="n"/>
+      <c r="AF29" s="509" t="n"/>
+      <c r="AG29" s="488" t="n"/>
+      <c r="AH29" s="488" t="n"/>
+      <c r="AI29" s="489" t="n"/>
+      <c r="AJ29" s="510" t="n"/>
+      <c r="AK29" s="488" t="n"/>
+      <c r="AL29" s="488" t="n"/>
+      <c r="AM29" s="488" t="n"/>
+      <c r="AN29" s="493" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1" s="264">
-      <c r="A30" s="497">
-        <f>ROW()-ROW($A$15)+1</f>
-        <v/>
-      </c>
-      <c r="B30" s="482" t="n"/>
-      <c r="C30" s="506" t="n"/>
-      <c r="D30" s="481" t="n"/>
-      <c r="E30" s="482" t="n"/>
-      <c r="F30" s="508" t="n"/>
-      <c r="G30" s="481" t="n"/>
-      <c r="H30" s="481" t="n"/>
-      <c r="I30" s="481" t="n"/>
-      <c r="J30" s="481" t="n"/>
-      <c r="K30" s="481" t="n"/>
-      <c r="L30" s="481" t="n"/>
-      <c r="M30" s="481" t="n"/>
-      <c r="N30" s="481" t="n"/>
-      <c r="O30" s="481" t="n"/>
-      <c r="P30" s="481" t="n"/>
-      <c r="Q30" s="481" t="n"/>
-      <c r="R30" s="481" t="n"/>
-      <c r="S30" s="481" t="n"/>
-      <c r="T30" s="481" t="n"/>
-      <c r="U30" s="482" t="n"/>
-      <c r="V30" s="506" t="n"/>
-      <c r="W30" s="481" t="n"/>
-      <c r="X30" s="481" t="n"/>
-      <c r="Y30" s="481" t="n"/>
-      <c r="Z30" s="481" t="n"/>
-      <c r="AA30" s="481" t="n"/>
-      <c r="AB30" s="481" t="n"/>
-      <c r="AC30" s="481" t="n"/>
-      <c r="AD30" s="481" t="n"/>
-      <c r="AE30" s="482" t="n"/>
-      <c r="AF30" s="501" t="n"/>
-      <c r="AG30" s="481" t="n"/>
-      <c r="AH30" s="481" t="n"/>
-      <c r="AI30" s="482" t="n"/>
-      <c r="AJ30" s="502" t="n"/>
-      <c r="AK30" s="481" t="n"/>
-      <c r="AL30" s="481" t="n"/>
-      <c r="AM30" s="481" t="n"/>
-      <c r="AN30" s="486" t="n"/>
+    <row r="30" ht="4" customHeight="1" s="264">
+      <c r="A30" s="519" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="26" t="n"/>
+      <c r="J30" s="26" t="n"/>
+      <c r="K30" s="26" t="n"/>
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="26" t="n"/>
+      <c r="N30" s="26" t="n"/>
+      <c r="O30" s="26" t="n"/>
+      <c r="P30" s="26" t="n"/>
+      <c r="Q30" s="26" t="n"/>
+      <c r="R30" s="26" t="n"/>
+      <c r="S30" s="26" t="n"/>
+      <c r="T30" s="26" t="n"/>
+      <c r="U30" s="26" t="n"/>
+      <c r="V30" s="26" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="26" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="26" t="n"/>
+      <c r="AB30" s="26" t="n"/>
+      <c r="AC30" s="26" t="n"/>
+      <c r="AD30" s="26" t="n"/>
+      <c r="AE30" s="26" t="n"/>
+      <c r="AF30" s="26" t="n"/>
+      <c r="AG30" s="26" t="n"/>
+      <c r="AH30" s="26" t="n"/>
+      <c r="AI30" s="26" t="n"/>
+      <c r="AJ30" s="26" t="n"/>
+      <c r="AK30" s="26" t="n"/>
+      <c r="AL30" s="26" t="n"/>
+      <c r="AM30" s="26" t="n"/>
+      <c r="AN30" s="26" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1" s="264">
-      <c r="A31" s="509">
-        <f>ROW()-ROW($A$15)+1</f>
-        <v/>
-      </c>
-      <c r="B31" s="489" t="n"/>
-      <c r="C31" s="510" t="n"/>
-      <c r="D31" s="488" t="n"/>
-      <c r="E31" s="489" t="n"/>
-      <c r="F31" s="511" t="n"/>
-      <c r="G31" s="488" t="n"/>
-      <c r="H31" s="488" t="n"/>
-      <c r="I31" s="488" t="n"/>
-      <c r="J31" s="488" t="n"/>
-      <c r="K31" s="488" t="n"/>
-      <c r="L31" s="488" t="n"/>
-      <c r="M31" s="488" t="n"/>
-      <c r="N31" s="488" t="n"/>
-      <c r="O31" s="488" t="n"/>
-      <c r="P31" s="488" t="n"/>
-      <c r="Q31" s="488" t="n"/>
-      <c r="R31" s="488" t="n"/>
-      <c r="S31" s="488" t="n"/>
-      <c r="T31" s="488" t="n"/>
-      <c r="U31" s="489" t="n"/>
-      <c r="V31" s="510" t="n"/>
-      <c r="W31" s="488" t="n"/>
-      <c r="X31" s="488" t="n"/>
-      <c r="Y31" s="488" t="n"/>
-      <c r="Z31" s="488" t="n"/>
-      <c r="AA31" s="488" t="n"/>
-      <c r="AB31" s="488" t="n"/>
-      <c r="AC31" s="488" t="n"/>
-      <c r="AD31" s="488" t="n"/>
-      <c r="AE31" s="489" t="n"/>
-      <c r="AF31" s="512" t="n"/>
-      <c r="AG31" s="488" t="n"/>
-      <c r="AH31" s="488" t="n"/>
-      <c r="AI31" s="489" t="n"/>
-      <c r="AJ31" s="513" t="n"/>
-      <c r="AK31" s="488" t="n"/>
-      <c r="AL31" s="488" t="n"/>
-      <c r="AM31" s="488" t="n"/>
-      <c r="AN31" s="493" t="n"/>
+    <row r="31" ht="17" customHeight="1" s="264">
+      <c r="A31" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3.  MACHINE RELEASE DECISION</t>
+        </is>
+      </c>
+      <c r="B31" s="471" t="n"/>
+      <c r="C31" s="471" t="n"/>
+      <c r="D31" s="471" t="n"/>
+      <c r="E31" s="471" t="n"/>
+      <c r="F31" s="471" t="n"/>
+      <c r="G31" s="471" t="n"/>
+      <c r="H31" s="471" t="n"/>
+      <c r="I31" s="471" t="n"/>
+      <c r="J31" s="471" t="n"/>
+      <c r="K31" s="471" t="n"/>
+      <c r="L31" s="471" t="n"/>
+      <c r="M31" s="471" t="n"/>
+      <c r="N31" s="471" t="n"/>
+      <c r="O31" s="471" t="n"/>
+      <c r="P31" s="471" t="n"/>
+      <c r="Q31" s="471" t="n"/>
+      <c r="R31" s="471" t="n"/>
+      <c r="S31" s="471" t="n"/>
+      <c r="T31" s="471" t="n"/>
+      <c r="U31" s="471" t="n"/>
+      <c r="V31" s="471" t="n"/>
+      <c r="W31" s="471" t="n"/>
+      <c r="X31" s="471" t="n"/>
+      <c r="Y31" s="471" t="n"/>
+      <c r="Z31" s="471" t="n"/>
+      <c r="AA31" s="471" t="n"/>
+      <c r="AB31" s="471" t="n"/>
+      <c r="AC31" s="471" t="n"/>
+      <c r="AD31" s="471" t="n"/>
+      <c r="AE31" s="471" t="n"/>
+      <c r="AF31" s="471" t="n"/>
+      <c r="AG31" s="471" t="n"/>
+      <c r="AH31" s="471" t="n"/>
+      <c r="AI31" s="471" t="n"/>
+      <c r="AJ31" s="471" t="n"/>
+      <c r="AK31" s="471" t="n"/>
+      <c r="AL31" s="471" t="n"/>
+      <c r="AM31" s="471" t="n"/>
+      <c r="AN31" s="472" t="n"/>
     </row>
-    <row r="32" ht="4" customHeight="1" s="264">
-      <c r="A32" s="522" t="n"/>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="26" t="n"/>
-      <c r="O32" s="26" t="n"/>
-      <c r="P32" s="26" t="n"/>
-      <c r="Q32" s="26" t="n"/>
-      <c r="R32" s="26" t="n"/>
-      <c r="S32" s="26" t="n"/>
-      <c r="T32" s="26" t="n"/>
-      <c r="U32" s="26" t="n"/>
-      <c r="V32" s="26" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="26" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="26" t="n"/>
-      <c r="AB32" s="26" t="n"/>
-      <c r="AC32" s="26" t="n"/>
-      <c r="AD32" s="26" t="n"/>
-      <c r="AE32" s="26" t="n"/>
-      <c r="AF32" s="26" t="n"/>
-      <c r="AG32" s="26" t="n"/>
-      <c r="AH32" s="26" t="n"/>
-      <c r="AI32" s="26" t="n"/>
-      <c r="AJ32" s="26" t="n"/>
-      <c r="AK32" s="26" t="n"/>
-      <c r="AL32" s="26" t="n"/>
-      <c r="AM32" s="26" t="n"/>
-      <c r="AN32" s="26" t="n"/>
+    <row r="32" ht="20" customHeight="1" s="264">
+      <c r="A32" s="473" t="inlineStr">
+        <is>
+          <t>Machine Status (Released / Hold-Maintenance)</t>
+        </is>
+      </c>
+      <c r="B32" s="474" t="n"/>
+      <c r="C32" s="474" t="n"/>
+      <c r="D32" s="474" t="n"/>
+      <c r="E32" s="474" t="n"/>
+      <c r="F32" s="474" t="n"/>
+      <c r="G32" s="475" t="n"/>
+      <c r="H32" s="476" t="n"/>
+      <c r="I32" s="474" t="n"/>
+      <c r="J32" s="474" t="n"/>
+      <c r="K32" s="474" t="n"/>
+      <c r="L32" s="474" t="n"/>
+      <c r="M32" s="474" t="n"/>
+      <c r="N32" s="474" t="n"/>
+      <c r="O32" s="474" t="n"/>
+      <c r="P32" s="474" t="n"/>
+      <c r="Q32" s="474" t="n"/>
+      <c r="R32" s="474" t="n"/>
+      <c r="S32" s="474" t="n"/>
+      <c r="T32" s="475" t="n"/>
+      <c r="U32" s="477" t="inlineStr">
+        <is>
+          <t>Maintenance Notified Ref</t>
+        </is>
+      </c>
+      <c r="V32" s="474" t="n"/>
+      <c r="W32" s="474" t="n"/>
+      <c r="X32" s="474" t="n"/>
+      <c r="Y32" s="474" t="n"/>
+      <c r="Z32" s="474" t="n"/>
+      <c r="AA32" s="475" t="n"/>
+      <c r="AB32" s="478" t="n"/>
+      <c r="AC32" s="474" t="n"/>
+      <c r="AD32" s="474" t="n"/>
+      <c r="AE32" s="474" t="n"/>
+      <c r="AF32" s="474" t="n"/>
+      <c r="AG32" s="474" t="n"/>
+      <c r="AH32" s="474" t="n"/>
+      <c r="AI32" s="474" t="n"/>
+      <c r="AJ32" s="474" t="n"/>
+      <c r="AK32" s="474" t="n"/>
+      <c r="AL32" s="474" t="n"/>
+      <c r="AM32" s="474" t="n"/>
+      <c r="AN32" s="479" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1" s="264">
-      <c r="A33" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3.  MACHINE STATUS / DISPOSITION</t>
-        </is>
-      </c>
-      <c r="B33" s="471" t="n"/>
-      <c r="C33" s="471" t="n"/>
-      <c r="D33" s="471" t="n"/>
-      <c r="E33" s="471" t="n"/>
-      <c r="F33" s="471" t="n"/>
-      <c r="G33" s="471" t="n"/>
-      <c r="H33" s="471" t="n"/>
-      <c r="I33" s="471" t="n"/>
-      <c r="J33" s="471" t="n"/>
-      <c r="K33" s="471" t="n"/>
-      <c r="L33" s="471" t="n"/>
-      <c r="M33" s="471" t="n"/>
-      <c r="N33" s="471" t="n"/>
-      <c r="O33" s="471" t="n"/>
-      <c r="P33" s="471" t="n"/>
-      <c r="Q33" s="471" t="n"/>
-      <c r="R33" s="471" t="n"/>
-      <c r="S33" s="471" t="n"/>
-      <c r="T33" s="471" t="n"/>
-      <c r="U33" s="471" t="n"/>
-      <c r="V33" s="471" t="n"/>
-      <c r="W33" s="471" t="n"/>
-      <c r="X33" s="471" t="n"/>
-      <c r="Y33" s="471" t="n"/>
-      <c r="Z33" s="471" t="n"/>
-      <c r="AA33" s="471" t="n"/>
-      <c r="AB33" s="471" t="n"/>
-      <c r="AC33" s="471" t="n"/>
-      <c r="AD33" s="471" t="n"/>
-      <c r="AE33" s="471" t="n"/>
-      <c r="AF33" s="471" t="n"/>
-      <c r="AG33" s="471" t="n"/>
-      <c r="AH33" s="471" t="n"/>
-      <c r="AI33" s="471" t="n"/>
-      <c r="AJ33" s="471" t="n"/>
-      <c r="AK33" s="471" t="n"/>
-      <c r="AL33" s="471" t="n"/>
-      <c r="AM33" s="471" t="n"/>
-      <c r="AN33" s="472" t="n"/>
+    <row r="33" ht="20" customHeight="1" s="264">
+      <c r="A33" s="487" t="inlineStr">
+        <is>
+          <t>Abnormality / Defect Noted</t>
+        </is>
+      </c>
+      <c r="B33" s="488" t="n"/>
+      <c r="C33" s="488" t="n"/>
+      <c r="D33" s="488" t="n"/>
+      <c r="E33" s="488" t="n"/>
+      <c r="F33" s="488" t="n"/>
+      <c r="G33" s="489" t="n"/>
+      <c r="H33" s="490" t="n"/>
+      <c r="I33" s="488" t="n"/>
+      <c r="J33" s="488" t="n"/>
+      <c r="K33" s="488" t="n"/>
+      <c r="L33" s="488" t="n"/>
+      <c r="M33" s="488" t="n"/>
+      <c r="N33" s="488" t="n"/>
+      <c r="O33" s="488" t="n"/>
+      <c r="P33" s="488" t="n"/>
+      <c r="Q33" s="488" t="n"/>
+      <c r="R33" s="488" t="n"/>
+      <c r="S33" s="488" t="n"/>
+      <c r="T33" s="489" t="n"/>
+      <c r="U33" s="491" t="inlineStr">
+        <is>
+          <t>Action Owner / Deadline</t>
+        </is>
+      </c>
+      <c r="V33" s="488" t="n"/>
+      <c r="W33" s="488" t="n"/>
+      <c r="X33" s="488" t="n"/>
+      <c r="Y33" s="488" t="n"/>
+      <c r="Z33" s="488" t="n"/>
+      <c r="AA33" s="489" t="n"/>
+      <c r="AB33" s="492" t="n"/>
+      <c r="AC33" s="488" t="n"/>
+      <c r="AD33" s="488" t="n"/>
+      <c r="AE33" s="488" t="n"/>
+      <c r="AF33" s="488" t="n"/>
+      <c r="AG33" s="488" t="n"/>
+      <c r="AH33" s="488" t="n"/>
+      <c r="AI33" s="488" t="n"/>
+      <c r="AJ33" s="488" t="n"/>
+      <c r="AK33" s="488" t="n"/>
+      <c r="AL33" s="488" t="n"/>
+      <c r="AM33" s="488" t="n"/>
+      <c r="AN33" s="493" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1" s="264">
-      <c r="A34" s="473" t="inlineStr">
-        <is>
-          <t>Machine Status (Released / Hold-Maintenance)</t>
-        </is>
-      </c>
-      <c r="B34" s="474" t="n"/>
-      <c r="C34" s="474" t="n"/>
-      <c r="D34" s="474" t="n"/>
-      <c r="E34" s="474" t="n"/>
-      <c r="F34" s="474" t="n"/>
-      <c r="G34" s="475" t="n"/>
-      <c r="H34" s="476" t="n"/>
-      <c r="I34" s="474" t="n"/>
-      <c r="J34" s="474" t="n"/>
-      <c r="K34" s="474" t="n"/>
-      <c r="L34" s="474" t="n"/>
-      <c r="M34" s="474" t="n"/>
-      <c r="N34" s="474" t="n"/>
-      <c r="O34" s="474" t="n"/>
-      <c r="P34" s="474" t="n"/>
-      <c r="Q34" s="474" t="n"/>
-      <c r="R34" s="474" t="n"/>
-      <c r="S34" s="474" t="n"/>
-      <c r="T34" s="475" t="n"/>
-      <c r="U34" s="477" t="inlineStr">
-        <is>
-          <t>Maintenance Notified Ref</t>
-        </is>
-      </c>
-      <c r="V34" s="474" t="n"/>
-      <c r="W34" s="474" t="n"/>
-      <c r="X34" s="474" t="n"/>
-      <c r="Y34" s="474" t="n"/>
-      <c r="Z34" s="474" t="n"/>
-      <c r="AA34" s="475" t="n"/>
-      <c r="AB34" s="478" t="n"/>
-      <c r="AC34" s="474" t="n"/>
-      <c r="AD34" s="474" t="n"/>
-      <c r="AE34" s="474" t="n"/>
-      <c r="AF34" s="474" t="n"/>
-      <c r="AG34" s="474" t="n"/>
-      <c r="AH34" s="474" t="n"/>
-      <c r="AI34" s="474" t="n"/>
-      <c r="AJ34" s="474" t="n"/>
-      <c r="AK34" s="474" t="n"/>
-      <c r="AL34" s="474" t="n"/>
-      <c r="AM34" s="474" t="n"/>
-      <c r="AN34" s="479" t="n"/>
+    <row r="34" ht="4" customHeight="1" s="264">
+      <c r="A34" s="519" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="26" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="26" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="26" t="n"/>
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="26" t="n"/>
+      <c r="N34" s="26" t="n"/>
+      <c r="O34" s="26" t="n"/>
+      <c r="P34" s="26" t="n"/>
+      <c r="Q34" s="26" t="n"/>
+      <c r="R34" s="26" t="n"/>
+      <c r="S34" s="26" t="n"/>
+      <c r="T34" s="26" t="n"/>
+      <c r="U34" s="26" t="n"/>
+      <c r="V34" s="26" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="26" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="26" t="n"/>
+      <c r="AB34" s="26" t="n"/>
+      <c r="AC34" s="26" t="n"/>
+      <c r="AD34" s="26" t="n"/>
+      <c r="AE34" s="26" t="n"/>
+      <c r="AF34" s="26" t="n"/>
+      <c r="AG34" s="26" t="n"/>
+      <c r="AH34" s="26" t="n"/>
+      <c r="AI34" s="26" t="n"/>
+      <c r="AJ34" s="26" t="n"/>
+      <c r="AK34" s="26" t="n"/>
+      <c r="AL34" s="26" t="n"/>
+      <c r="AM34" s="26" t="n"/>
+      <c r="AN34" s="26" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1" s="264">
-      <c r="A35" s="487" t="inlineStr">
-        <is>
-          <t>Abnormality / Defect Noted</t>
-        </is>
-      </c>
-      <c r="B35" s="488" t="n"/>
-      <c r="C35" s="488" t="n"/>
-      <c r="D35" s="488" t="n"/>
-      <c r="E35" s="488" t="n"/>
-      <c r="F35" s="488" t="n"/>
-      <c r="G35" s="489" t="n"/>
-      <c r="H35" s="490" t="n"/>
-      <c r="I35" s="488" t="n"/>
-      <c r="J35" s="488" t="n"/>
-      <c r="K35" s="488" t="n"/>
-      <c r="L35" s="488" t="n"/>
-      <c r="M35" s="488" t="n"/>
-      <c r="N35" s="488" t="n"/>
-      <c r="O35" s="488" t="n"/>
-      <c r="P35" s="488" t="n"/>
-      <c r="Q35" s="488" t="n"/>
-      <c r="R35" s="488" t="n"/>
-      <c r="S35" s="488" t="n"/>
-      <c r="T35" s="489" t="n"/>
-      <c r="U35" s="491" t="inlineStr">
-        <is>
-          <t>Action Owner / Deadline</t>
-        </is>
-      </c>
-      <c r="V35" s="488" t="n"/>
-      <c r="W35" s="488" t="n"/>
-      <c r="X35" s="488" t="n"/>
-      <c r="Y35" s="488" t="n"/>
-      <c r="Z35" s="488" t="n"/>
-      <c r="AA35" s="489" t="n"/>
-      <c r="AB35" s="492" t="n"/>
-      <c r="AC35" s="488" t="n"/>
-      <c r="AD35" s="488" t="n"/>
-      <c r="AE35" s="488" t="n"/>
-      <c r="AF35" s="488" t="n"/>
-      <c r="AG35" s="488" t="n"/>
-      <c r="AH35" s="488" t="n"/>
-      <c r="AI35" s="488" t="n"/>
-      <c r="AJ35" s="488" t="n"/>
-      <c r="AK35" s="488" t="n"/>
-      <c r="AL35" s="488" t="n"/>
-      <c r="AM35" s="488" t="n"/>
-      <c r="AN35" s="493" t="n"/>
+    <row r="35" ht="17" customHeight="1" s="264">
+      <c r="A35" s="470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4.  APPROVAL</t>
+        </is>
+      </c>
+      <c r="B35" s="471" t="n"/>
+      <c r="C35" s="471" t="n"/>
+      <c r="D35" s="471" t="n"/>
+      <c r="E35" s="471" t="n"/>
+      <c r="F35" s="471" t="n"/>
+      <c r="G35" s="471" t="n"/>
+      <c r="H35" s="471" t="n"/>
+      <c r="I35" s="471" t="n"/>
+      <c r="J35" s="471" t="n"/>
+      <c r="K35" s="471" t="n"/>
+      <c r="L35" s="471" t="n"/>
+      <c r="M35" s="471" t="n"/>
+      <c r="N35" s="471" t="n"/>
+      <c r="O35" s="471" t="n"/>
+      <c r="P35" s="471" t="n"/>
+      <c r="Q35" s="471" t="n"/>
+      <c r="R35" s="471" t="n"/>
+      <c r="S35" s="471" t="n"/>
+      <c r="T35" s="471" t="n"/>
+      <c r="U35" s="471" t="n"/>
+      <c r="V35" s="471" t="n"/>
+      <c r="W35" s="471" t="n"/>
+      <c r="X35" s="471" t="n"/>
+      <c r="Y35" s="471" t="n"/>
+      <c r="Z35" s="471" t="n"/>
+      <c r="AA35" s="471" t="n"/>
+      <c r="AB35" s="471" t="n"/>
+      <c r="AC35" s="471" t="n"/>
+      <c r="AD35" s="471" t="n"/>
+      <c r="AE35" s="471" t="n"/>
+      <c r="AF35" s="471" t="n"/>
+      <c r="AG35" s="471" t="n"/>
+      <c r="AH35" s="471" t="n"/>
+      <c r="AI35" s="471" t="n"/>
+      <c r="AJ35" s="471" t="n"/>
+      <c r="AK35" s="471" t="n"/>
+      <c r="AL35" s="471" t="n"/>
+      <c r="AM35" s="471" t="n"/>
+      <c r="AN35" s="472" t="n"/>
     </row>
-    <row r="36" ht="4" customHeight="1" s="264">
-      <c r="A36" s="522" t="n"/>
-      <c r="B36" s="26" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="26" t="n"/>
-      <c r="L36" s="26" t="n"/>
-      <c r="M36" s="26" t="n"/>
-      <c r="N36" s="26" t="n"/>
-      <c r="O36" s="26" t="n"/>
-      <c r="P36" s="26" t="n"/>
-      <c r="Q36" s="26" t="n"/>
-      <c r="R36" s="26" t="n"/>
-      <c r="S36" s="26" t="n"/>
-      <c r="T36" s="26" t="n"/>
-      <c r="U36" s="26" t="n"/>
-      <c r="V36" s="26" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="26" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="26" t="n"/>
-      <c r="AB36" s="26" t="n"/>
-      <c r="AC36" s="26" t="n"/>
-      <c r="AD36" s="26" t="n"/>
-      <c r="AE36" s="26" t="n"/>
-      <c r="AF36" s="26" t="n"/>
-      <c r="AG36" s="26" t="n"/>
-      <c r="AH36" s="26" t="n"/>
-      <c r="AI36" s="26" t="n"/>
-      <c r="AJ36" s="26" t="n"/>
-      <c r="AK36" s="26" t="n"/>
-      <c r="AL36" s="26" t="n"/>
-      <c r="AM36" s="26" t="n"/>
-      <c r="AN36" s="26" t="n"/>
+    <row r="36" ht="17" customHeight="1" s="264">
+      <c r="A36" s="511" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="B36" s="471" t="n"/>
+      <c r="C36" s="471" t="n"/>
+      <c r="D36" s="471" t="n"/>
+      <c r="E36" s="471" t="n"/>
+      <c r="F36" s="471" t="n"/>
+      <c r="G36" s="471" t="n"/>
+      <c r="H36" s="471" t="n"/>
+      <c r="I36" s="471" t="n"/>
+      <c r="J36" s="471" t="n"/>
+      <c r="K36" s="471" t="n"/>
+      <c r="L36" s="471" t="n"/>
+      <c r="M36" s="472" t="n"/>
+      <c r="N36" s="511" t="inlineStr">
+        <is>
+          <t>Shift Leader</t>
+        </is>
+      </c>
+      <c r="O36" s="471" t="n"/>
+      <c r="P36" s="471" t="n"/>
+      <c r="Q36" s="471" t="n"/>
+      <c r="R36" s="471" t="n"/>
+      <c r="S36" s="471" t="n"/>
+      <c r="T36" s="471" t="n"/>
+      <c r="U36" s="471" t="n"/>
+      <c r="V36" s="471" t="n"/>
+      <c r="W36" s="471" t="n"/>
+      <c r="X36" s="471" t="n"/>
+      <c r="Y36" s="471" t="n"/>
+      <c r="Z36" s="472" t="n"/>
+      <c r="AA36" s="511" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="AB36" s="471" t="n"/>
+      <c r="AC36" s="471" t="n"/>
+      <c r="AD36" s="471" t="n"/>
+      <c r="AE36" s="471" t="n"/>
+      <c r="AF36" s="471" t="n"/>
+      <c r="AG36" s="471" t="n"/>
+      <c r="AH36" s="471" t="n"/>
+      <c r="AI36" s="471" t="n"/>
+      <c r="AJ36" s="471" t="n"/>
+      <c r="AK36" s="471" t="n"/>
+      <c r="AL36" s="471" t="n"/>
+      <c r="AM36" s="471" t="n"/>
+      <c r="AN36" s="472" t="n"/>
     </row>
-    <row r="37" ht="17" customHeight="1" s="264">
-      <c r="A37" s="470" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4.  APPROVAL</t>
-        </is>
-      </c>
-      <c r="B37" s="471" t="n"/>
-      <c r="C37" s="471" t="n"/>
-      <c r="D37" s="471" t="n"/>
-      <c r="E37" s="471" t="n"/>
-      <c r="F37" s="471" t="n"/>
-      <c r="G37" s="471" t="n"/>
-      <c r="H37" s="471" t="n"/>
-      <c r="I37" s="471" t="n"/>
-      <c r="J37" s="471" t="n"/>
-      <c r="K37" s="471" t="n"/>
-      <c r="L37" s="471" t="n"/>
-      <c r="M37" s="471" t="n"/>
-      <c r="N37" s="471" t="n"/>
-      <c r="O37" s="471" t="n"/>
-      <c r="P37" s="471" t="n"/>
-      <c r="Q37" s="471" t="n"/>
-      <c r="R37" s="471" t="n"/>
-      <c r="S37" s="471" t="n"/>
-      <c r="T37" s="471" t="n"/>
-      <c r="U37" s="471" t="n"/>
-      <c r="V37" s="471" t="n"/>
-      <c r="W37" s="471" t="n"/>
-      <c r="X37" s="471" t="n"/>
-      <c r="Y37" s="471" t="n"/>
-      <c r="Z37" s="471" t="n"/>
-      <c r="AA37" s="471" t="n"/>
-      <c r="AB37" s="471" t="n"/>
-      <c r="AC37" s="471" t="n"/>
-      <c r="AD37" s="471" t="n"/>
-      <c r="AE37" s="471" t="n"/>
-      <c r="AF37" s="471" t="n"/>
-      <c r="AG37" s="471" t="n"/>
-      <c r="AH37" s="471" t="n"/>
-      <c r="AI37" s="471" t="n"/>
-      <c r="AJ37" s="471" t="n"/>
-      <c r="AK37" s="471" t="n"/>
-      <c r="AL37" s="471" t="n"/>
-      <c r="AM37" s="471" t="n"/>
-      <c r="AN37" s="472" t="n"/>
+    <row r="37" ht="26" customHeight="1" s="264">
+      <c r="A37" s="512" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="B37" s="513" t="n"/>
+      <c r="C37" s="513" t="n"/>
+      <c r="D37" s="513" t="n"/>
+      <c r="E37" s="513" t="n"/>
+      <c r="F37" s="513" t="n"/>
+      <c r="G37" s="513" t="n"/>
+      <c r="H37" s="513" t="n"/>
+      <c r="I37" s="513" t="n"/>
+      <c r="J37" s="513" t="n"/>
+      <c r="K37" s="513" t="n"/>
+      <c r="L37" s="513" t="n"/>
+      <c r="M37" s="514" t="n"/>
+      <c r="N37" s="512" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="O37" s="513" t="n"/>
+      <c r="P37" s="513" t="n"/>
+      <c r="Q37" s="513" t="n"/>
+      <c r="R37" s="513" t="n"/>
+      <c r="S37" s="513" t="n"/>
+      <c r="T37" s="513" t="n"/>
+      <c r="U37" s="513" t="n"/>
+      <c r="V37" s="513" t="n"/>
+      <c r="W37" s="513" t="n"/>
+      <c r="X37" s="513" t="n"/>
+      <c r="Y37" s="513" t="n"/>
+      <c r="Z37" s="514" t="n"/>
+      <c r="AA37" s="512" t="inlineStr">
+        <is>
+          <t>Name  /  Signature  /  Date</t>
+        </is>
+      </c>
+      <c r="AB37" s="513" t="n"/>
+      <c r="AC37" s="513" t="n"/>
+      <c r="AD37" s="513" t="n"/>
+      <c r="AE37" s="513" t="n"/>
+      <c r="AF37" s="513" t="n"/>
+      <c r="AG37" s="513" t="n"/>
+      <c r="AH37" s="513" t="n"/>
+      <c r="AI37" s="513" t="n"/>
+      <c r="AJ37" s="513" t="n"/>
+      <c r="AK37" s="513" t="n"/>
+      <c r="AL37" s="513" t="n"/>
+      <c r="AM37" s="513" t="n"/>
+      <c r="AN37" s="514" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1" s="264">
-      <c r="A38" s="514" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="B38" s="471" t="n"/>
-      <c r="C38" s="471" t="n"/>
-      <c r="D38" s="471" t="n"/>
-      <c r="E38" s="471" t="n"/>
-      <c r="F38" s="471" t="n"/>
-      <c r="G38" s="471" t="n"/>
-      <c r="H38" s="471" t="n"/>
-      <c r="I38" s="471" t="n"/>
-      <c r="J38" s="471" t="n"/>
-      <c r="K38" s="471" t="n"/>
-      <c r="L38" s="471" t="n"/>
-      <c r="M38" s="472" t="n"/>
-      <c r="N38" s="514" t="inlineStr">
-        <is>
-          <t>Shift Leader</t>
-        </is>
-      </c>
-      <c r="O38" s="471" t="n"/>
-      <c r="P38" s="471" t="n"/>
-      <c r="Q38" s="471" t="n"/>
-      <c r="R38" s="471" t="n"/>
-      <c r="S38" s="471" t="n"/>
-      <c r="T38" s="471" t="n"/>
-      <c r="U38" s="471" t="n"/>
-      <c r="V38" s="471" t="n"/>
-      <c r="W38" s="471" t="n"/>
-      <c r="X38" s="471" t="n"/>
-      <c r="Y38" s="471" t="n"/>
-      <c r="Z38" s="472" t="n"/>
-      <c r="AA38" s="514" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="AB38" s="471" t="n"/>
-      <c r="AC38" s="471" t="n"/>
-      <c r="AD38" s="471" t="n"/>
-      <c r="AE38" s="471" t="n"/>
-      <c r="AF38" s="471" t="n"/>
-      <c r="AG38" s="471" t="n"/>
-      <c r="AH38" s="471" t="n"/>
-      <c r="AI38" s="471" t="n"/>
-      <c r="AJ38" s="471" t="n"/>
-      <c r="AK38" s="471" t="n"/>
-      <c r="AL38" s="471" t="n"/>
-      <c r="AM38" s="471" t="n"/>
-      <c r="AN38" s="472" t="n"/>
+    <row r="38" ht="26" customHeight="1" s="264">
+      <c r="A38" s="515" t="n"/>
+      <c r="M38" s="516" t="n"/>
+      <c r="N38" s="515" t="n"/>
+      <c r="Z38" s="516" t="n"/>
+      <c r="AA38" s="515" t="n"/>
+      <c r="AN38" s="516" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="264">
-      <c r="A39" s="515" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="B39" s="516" t="n"/>
-      <c r="C39" s="516" t="n"/>
-      <c r="D39" s="516" t="n"/>
-      <c r="E39" s="516" t="n"/>
-      <c r="F39" s="516" t="n"/>
-      <c r="G39" s="516" t="n"/>
-      <c r="H39" s="516" t="n"/>
-      <c r="I39" s="516" t="n"/>
-      <c r="J39" s="516" t="n"/>
-      <c r="K39" s="516" t="n"/>
-      <c r="L39" s="516" t="n"/>
-      <c r="M39" s="517" t="n"/>
-      <c r="N39" s="515" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="O39" s="516" t="n"/>
-      <c r="P39" s="516" t="n"/>
-      <c r="Q39" s="516" t="n"/>
-      <c r="R39" s="516" t="n"/>
-      <c r="S39" s="516" t="n"/>
-      <c r="T39" s="516" t="n"/>
-      <c r="U39" s="516" t="n"/>
-      <c r="V39" s="516" t="n"/>
-      <c r="W39" s="516" t="n"/>
-      <c r="X39" s="516" t="n"/>
-      <c r="Y39" s="516" t="n"/>
-      <c r="Z39" s="517" t="n"/>
-      <c r="AA39" s="515" t="inlineStr">
-        <is>
-          <t>Name  /  Signature  /  Date</t>
-        </is>
-      </c>
-      <c r="AB39" s="516" t="n"/>
-      <c r="AC39" s="516" t="n"/>
-      <c r="AD39" s="516" t="n"/>
-      <c r="AE39" s="516" t="n"/>
-      <c r="AF39" s="516" t="n"/>
-      <c r="AG39" s="516" t="n"/>
-      <c r="AH39" s="516" t="n"/>
-      <c r="AI39" s="516" t="n"/>
-      <c r="AJ39" s="516" t="n"/>
-      <c r="AK39" s="516" t="n"/>
-      <c r="AL39" s="516" t="n"/>
-      <c r="AM39" s="516" t="n"/>
-      <c r="AN39" s="517" t="n"/>
+      <c r="A39" s="517" t="n"/>
+      <c r="B39" s="488" t="n"/>
+      <c r="C39" s="488" t="n"/>
+      <c r="D39" s="488" t="n"/>
+      <c r="E39" s="488" t="n"/>
+      <c r="F39" s="488" t="n"/>
+      <c r="G39" s="488" t="n"/>
+      <c r="H39" s="488" t="n"/>
+      <c r="I39" s="488" t="n"/>
+      <c r="J39" s="488" t="n"/>
+      <c r="K39" s="488" t="n"/>
+      <c r="L39" s="488" t="n"/>
+      <c r="M39" s="493" t="n"/>
+      <c r="N39" s="517" t="n"/>
+      <c r="O39" s="488" t="n"/>
+      <c r="P39" s="488" t="n"/>
+      <c r="Q39" s="488" t="n"/>
+      <c r="R39" s="488" t="n"/>
+      <c r="S39" s="488" t="n"/>
+      <c r="T39" s="488" t="n"/>
+      <c r="U39" s="488" t="n"/>
+      <c r="V39" s="488" t="n"/>
+      <c r="W39" s="488" t="n"/>
+      <c r="X39" s="488" t="n"/>
+      <c r="Y39" s="488" t="n"/>
+      <c r="Z39" s="493" t="n"/>
+      <c r="AA39" s="517" t="n"/>
+      <c r="AB39" s="488" t="n"/>
+      <c r="AC39" s="488" t="n"/>
+      <c r="AD39" s="488" t="n"/>
+      <c r="AE39" s="488" t="n"/>
+      <c r="AF39" s="488" t="n"/>
+      <c r="AG39" s="488" t="n"/>
+      <c r="AH39" s="488" t="n"/>
+      <c r="AI39" s="488" t="n"/>
+      <c r="AJ39" s="488" t="n"/>
+      <c r="AK39" s="488" t="n"/>
+      <c r="AL39" s="488" t="n"/>
+      <c r="AM39" s="488" t="n"/>
+      <c r="AN39" s="493" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1" s="264">
-      <c r="A40" s="518" t="n"/>
-      <c r="M40" s="519" t="n"/>
-      <c r="N40" s="518" t="n"/>
-      <c r="Z40" s="519" t="n"/>
-      <c r="AA40" s="518" t="n"/>
-      <c r="AN40" s="519" t="n"/>
+    <row r="40" ht="4" customHeight="1" s="264">
+      <c r="A40" s="519" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
+      <c r="M40" s="26" t="n"/>
+      <c r="N40" s="26" t="n"/>
+      <c r="O40" s="26" t="n"/>
+      <c r="P40" s="26" t="n"/>
+      <c r="Q40" s="26" t="n"/>
+      <c r="R40" s="26" t="n"/>
+      <c r="S40" s="26" t="n"/>
+      <c r="T40" s="26" t="n"/>
+      <c r="U40" s="26" t="n"/>
+      <c r="V40" s="26" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="26" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="26" t="n"/>
+      <c r="AB40" s="26" t="n"/>
+      <c r="AC40" s="26" t="n"/>
+      <c r="AD40" s="26" t="n"/>
+      <c r="AE40" s="26" t="n"/>
+      <c r="AF40" s="26" t="n"/>
+      <c r="AG40" s="26" t="n"/>
+      <c r="AH40" s="26" t="n"/>
+      <c r="AI40" s="26" t="n"/>
+      <c r="AJ40" s="26" t="n"/>
+      <c r="AK40" s="26" t="n"/>
+      <c r="AL40" s="26" t="n"/>
+      <c r="AM40" s="26" t="n"/>
+      <c r="AN40" s="26" t="n"/>
     </row>
-    <row r="41" ht="26" customHeight="1" s="264">
-      <c r="A41" s="520" t="n"/>
-      <c r="B41" s="488" t="n"/>
-      <c r="C41" s="488" t="n"/>
-      <c r="D41" s="488" t="n"/>
-      <c r="E41" s="488" t="n"/>
-      <c r="F41" s="488" t="n"/>
-      <c r="G41" s="488" t="n"/>
-      <c r="H41" s="488" t="n"/>
-      <c r="I41" s="488" t="n"/>
-      <c r="J41" s="488" t="n"/>
-      <c r="K41" s="488" t="n"/>
-      <c r="L41" s="488" t="n"/>
-      <c r="M41" s="493" t="n"/>
-      <c r="N41" s="520" t="n"/>
-      <c r="O41" s="488" t="n"/>
-      <c r="P41" s="488" t="n"/>
-      <c r="Q41" s="488" t="n"/>
-      <c r="R41" s="488" t="n"/>
-      <c r="S41" s="488" t="n"/>
-      <c r="T41" s="488" t="n"/>
-      <c r="U41" s="488" t="n"/>
-      <c r="V41" s="488" t="n"/>
-      <c r="W41" s="488" t="n"/>
-      <c r="X41" s="488" t="n"/>
-      <c r="Y41" s="488" t="n"/>
-      <c r="Z41" s="493" t="n"/>
-      <c r="AA41" s="520" t="n"/>
-      <c r="AB41" s="488" t="n"/>
-      <c r="AC41" s="488" t="n"/>
-      <c r="AD41" s="488" t="n"/>
-      <c r="AE41" s="488" t="n"/>
-      <c r="AF41" s="488" t="n"/>
-      <c r="AG41" s="488" t="n"/>
-      <c r="AH41" s="488" t="n"/>
-      <c r="AI41" s="488" t="n"/>
-      <c r="AJ41" s="488" t="n"/>
-      <c r="AK41" s="488" t="n"/>
-      <c r="AL41" s="488" t="n"/>
-      <c r="AM41" s="488" t="n"/>
-      <c r="AN41" s="493" t="n"/>
-    </row>
-    <row r="42" ht="4" customHeight="1" s="264">
-      <c r="A42" s="522" t="n"/>
-      <c r="B42" s="26" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="n"/>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n"/>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="26" t="n"/>
-      <c r="P42" s="26" t="n"/>
-      <c r="Q42" s="26" t="n"/>
-      <c r="R42" s="26" t="n"/>
-      <c r="S42" s="26" t="n"/>
-      <c r="T42" s="26" t="n"/>
-      <c r="U42" s="26" t="n"/>
-      <c r="V42" s="26" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="26" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="26" t="n"/>
-      <c r="AB42" s="26" t="n"/>
-      <c r="AC42" s="26" t="n"/>
-      <c r="AD42" s="26" t="n"/>
-      <c r="AE42" s="26" t="n"/>
-      <c r="AF42" s="26" t="n"/>
-      <c r="AG42" s="26" t="n"/>
-      <c r="AH42" s="26" t="n"/>
-      <c r="AI42" s="26" t="n"/>
-      <c r="AJ42" s="26" t="n"/>
-      <c r="AK42" s="26" t="n"/>
-      <c r="AL42" s="26" t="n"/>
-      <c r="AM42" s="26" t="n"/>
-      <c r="AN42" s="26" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" s="264">
-      <c r="A43" s="521" t="inlineStr">
-        <is>
-          <t>NOTICE — Complete this check before first production run each shift. Any FAIL item holds the machine until Maintenance clears it. Ref: SOP-503 / FRM-521. Retain: 3 years.</t>
-        </is>
-      </c>
-      <c r="B43" s="471" t="n"/>
-      <c r="C43" s="471" t="n"/>
-      <c r="D43" s="471" t="n"/>
-      <c r="E43" s="471" t="n"/>
-      <c r="F43" s="471" t="n"/>
-      <c r="G43" s="471" t="n"/>
-      <c r="H43" s="471" t="n"/>
-      <c r="I43" s="471" t="n"/>
-      <c r="J43" s="471" t="n"/>
-      <c r="K43" s="471" t="n"/>
-      <c r="L43" s="471" t="n"/>
-      <c r="M43" s="471" t="n"/>
-      <c r="N43" s="471" t="n"/>
-      <c r="O43" s="471" t="n"/>
-      <c r="P43" s="471" t="n"/>
-      <c r="Q43" s="471" t="n"/>
-      <c r="R43" s="471" t="n"/>
-      <c r="S43" s="471" t="n"/>
-      <c r="T43" s="471" t="n"/>
-      <c r="U43" s="471" t="n"/>
-      <c r="V43" s="471" t="n"/>
-      <c r="W43" s="471" t="n"/>
-      <c r="X43" s="471" t="n"/>
-      <c r="Y43" s="471" t="n"/>
-      <c r="Z43" s="471" t="n"/>
-      <c r="AA43" s="471" t="n"/>
-      <c r="AB43" s="471" t="n"/>
-      <c r="AC43" s="471" t="n"/>
-      <c r="AD43" s="471" t="n"/>
-      <c r="AE43" s="471" t="n"/>
-      <c r="AF43" s="471" t="n"/>
-      <c r="AG43" s="471" t="n"/>
-      <c r="AH43" s="471" t="n"/>
-      <c r="AI43" s="471" t="n"/>
-      <c r="AJ43" s="471" t="n"/>
-      <c r="AK43" s="471" t="n"/>
-      <c r="AL43" s="471" t="n"/>
-      <c r="AM43" s="471" t="n"/>
-      <c r="AN43" s="472" t="n"/>
+    <row r="41" ht="24" customHeight="1" s="264">
+      <c r="A41" s="518" t="inlineStr">
+        <is>
+          <t>NOTICE — Complete this check before the first production run each shift. Any FAIL item holds the machine until Maintenance clears it. Ref: SOP-503 / FRM-521. Retain: 3 years. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
+        </is>
+      </c>
+      <c r="B41" s="471" t="n"/>
+      <c r="C41" s="471" t="n"/>
+      <c r="D41" s="471" t="n"/>
+      <c r="E41" s="471" t="n"/>
+      <c r="F41" s="471" t="n"/>
+      <c r="G41" s="471" t="n"/>
+      <c r="H41" s="471" t="n"/>
+      <c r="I41" s="471" t="n"/>
+      <c r="J41" s="471" t="n"/>
+      <c r="K41" s="471" t="n"/>
+      <c r="L41" s="471" t="n"/>
+      <c r="M41" s="471" t="n"/>
+      <c r="N41" s="471" t="n"/>
+      <c r="O41" s="471" t="n"/>
+      <c r="P41" s="471" t="n"/>
+      <c r="Q41" s="471" t="n"/>
+      <c r="R41" s="471" t="n"/>
+      <c r="S41" s="471" t="n"/>
+      <c r="T41" s="471" t="n"/>
+      <c r="U41" s="471" t="n"/>
+      <c r="V41" s="471" t="n"/>
+      <c r="W41" s="471" t="n"/>
+      <c r="X41" s="471" t="n"/>
+      <c r="Y41" s="471" t="n"/>
+      <c r="Z41" s="471" t="n"/>
+      <c r="AA41" s="471" t="n"/>
+      <c r="AB41" s="471" t="n"/>
+      <c r="AC41" s="471" t="n"/>
+      <c r="AD41" s="471" t="n"/>
+      <c r="AE41" s="471" t="n"/>
+      <c r="AF41" s="471" t="n"/>
+      <c r="AG41" s="471" t="n"/>
+      <c r="AH41" s="471" t="n"/>
+      <c r="AI41" s="471" t="n"/>
+      <c r="AJ41" s="471" t="n"/>
+      <c r="AK41" s="471" t="n"/>
+      <c r="AL41" s="471" t="n"/>
+      <c r="AM41" s="471" t="n"/>
+      <c r="AN41" s="472" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="144">
+    <mergeCell ref="U33:AA33"/>
     <mergeCell ref="F23:U23"/>
-    <mergeCell ref="A12:AN12"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A35:G35"/>
     <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A32:AN32"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A14:AN14"/>
+    <mergeCell ref="H33:T33"/>
     <mergeCell ref="V22:AE22"/>
-    <mergeCell ref="AB34:AN34"/>
     <mergeCell ref="AF22:AI22"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="AE4:AH4"/>
     <mergeCell ref="AF18:AI18"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="U9:AA9"/>
-    <mergeCell ref="A43:AN43"/>
+    <mergeCell ref="N36:Z36"/>
     <mergeCell ref="V21:AE21"/>
-    <mergeCell ref="H35:T35"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A40:AN40"/>
     <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="V14:AE14"/>
     <mergeCell ref="F19:U19"/>
     <mergeCell ref="V23:AE23"/>
     <mergeCell ref="H9:T9"/>
     <mergeCell ref="I2:AD4"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="F30:U30"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="F20:U20"/>
+    <mergeCell ref="U32:AA32"/>
+    <mergeCell ref="N37:Z39"/>
     <mergeCell ref="A2:H6"/>
     <mergeCell ref="AJ20:AN20"/>
     <mergeCell ref="A19:B19"/>
@@ -7498,15 +7445,11 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="F17:U17"/>
     <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="N39:Z41"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="N38:Z38"/>
     <mergeCell ref="AJ22:AN22"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="AJ31:AN31"/>
+    <mergeCell ref="H32:T32"/>
     <mergeCell ref="V27:AE27"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="F31:U31"/>
     <mergeCell ref="F28:U28"/>
     <mergeCell ref="AF26:AI26"/>
     <mergeCell ref="AJ21:AN21"/>
@@ -7514,82 +7457,76 @@
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="V25:AE25"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="AJ14:AN14"/>
     <mergeCell ref="AE5:AH5"/>
     <mergeCell ref="AJ23:AN23"/>
     <mergeCell ref="U10:AA10"/>
     <mergeCell ref="AB10:AN10"/>
     <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AB33:AN33"/>
     <mergeCell ref="V17:AE17"/>
-    <mergeCell ref="U34:AA34"/>
     <mergeCell ref="A13:AN13"/>
     <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AA36:AN36"/>
     <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="A31:AN31"/>
     <mergeCell ref="H10:T10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="AA39:AN41"/>
     <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="V20:AE20"/>
-    <mergeCell ref="H34:T34"/>
     <mergeCell ref="V29:AE29"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="AF16:AI16"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="AF25:AI25"/>
     <mergeCell ref="AJ26:AN26"/>
-    <mergeCell ref="V31:AE31"/>
     <mergeCell ref="F18:U18"/>
     <mergeCell ref="A7:AN7"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="A41:AN41"/>
     <mergeCell ref="AJ25:AN25"/>
+    <mergeCell ref="U12:AA12"/>
     <mergeCell ref="V15:AE15"/>
+    <mergeCell ref="AB12:AN12"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AF14:AI14"/>
     <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="F22:U22"/>
     <mergeCell ref="V26:AE26"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="A33:AN33"/>
-    <mergeCell ref="A42:AN42"/>
+    <mergeCell ref="H12:T12"/>
     <mergeCell ref="V16:AE16"/>
     <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="F14:U14"/>
+    <mergeCell ref="A35:AN35"/>
     <mergeCell ref="V18:AE18"/>
-    <mergeCell ref="U35:AA35"/>
     <mergeCell ref="I6:AD6"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="AI2:AN2"/>
-    <mergeCell ref="A39:M41"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A30:AN30"/>
+    <mergeCell ref="AB32:AN32"/>
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AB35:AN35"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="AJ24:AN24"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="F24:U24"/>
     <mergeCell ref="U11:AA11"/>
     <mergeCell ref="F21:U21"/>
     <mergeCell ref="V28:AE28"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="AB9:AN9"/>
     <mergeCell ref="F26:U26"/>
-    <mergeCell ref="V30:AE30"/>
-    <mergeCell ref="A37:AN37"/>
     <mergeCell ref="H11:T11"/>
+    <mergeCell ref="A37:M39"/>
     <mergeCell ref="AB11:AN11"/>
     <mergeCell ref="AI6:AN6"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="AF17:AI17"/>
     <mergeCell ref="F27:U27"/>
-    <mergeCell ref="AA38:AN38"/>
     <mergeCell ref="AJ27:AN27"/>
     <mergeCell ref="AI4:AN4"/>
     <mergeCell ref="A8:AN8"/>
+    <mergeCell ref="AA37:AN39"/>
     <mergeCell ref="AJ17:AN17"/>
     <mergeCell ref="AF19:AI19"/>
     <mergeCell ref="A16:B16"/>
@@ -7602,11 +7539,10 @@
     <mergeCell ref="F29:U29"/>
     <mergeCell ref="F16:U16"/>
     <mergeCell ref="F25:U25"/>
+    <mergeCell ref="A34:AN34"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="AJ30:AN30"/>
     <mergeCell ref="AF29:AI29"/>
     <mergeCell ref="AE2:AH2"/>
-    <mergeCell ref="A36:AN36"/>
     <mergeCell ref="F15:U15"/>
     <mergeCell ref="V24:AE24"/>
     <mergeCell ref="V19:AE19"/>
@@ -7614,9 +7550,9 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="AF21:AI21"/>
     <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
-  <conditionalFormatting sqref="AF15:AF31">
+  <conditionalFormatting sqref="AF16:AF29">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -7628,13 +7564,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AF15 AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29 AF30 AF31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25 AF26 AF27 AF28 AF29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=LISTS!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
